--- a/artfynd/A 14786-2026 artfynd.xlsx
+++ b/artfynd/A 14786-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135558676</v>
       </c>
       <c r="B2" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135558885</v>
       </c>
       <c r="B3" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135559348</v>
       </c>
       <c r="B4" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135559561</v>
       </c>
       <c r="B5" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135559640</v>
       </c>
       <c r="B6" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135559895</v>
       </c>
       <c r="B7" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135558813</v>
       </c>
       <c r="B8" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135558533</v>
       </c>
       <c r="B9" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135558956</v>
       </c>
       <c r="B10" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135558472</v>
       </c>
       <c r="B11" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135558865</v>
       </c>
       <c r="B12" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 14786-2026 artfynd.xlsx
+++ b/artfynd/A 14786-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135558676</v>
       </c>
       <c r="B2" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135558885</v>
       </c>
       <c r="B3" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135559348</v>
       </c>
       <c r="B4" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135559561</v>
       </c>
       <c r="B5" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135559640</v>
       </c>
       <c r="B6" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135559895</v>
       </c>
       <c r="B7" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135558813</v>
       </c>
       <c r="B8" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135558533</v>
       </c>
       <c r="B9" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135558956</v>
       </c>
       <c r="B10" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135558472</v>
       </c>
       <c r="B11" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135558865</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 14786-2026 artfynd.xlsx
+++ b/artfynd/A 14786-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135558676</v>
       </c>
       <c r="B2" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135558885</v>
       </c>
       <c r="B3" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135559348</v>
       </c>
       <c r="B4" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135559561</v>
       </c>
       <c r="B5" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135559640</v>
       </c>
       <c r="B6" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135559895</v>
       </c>
       <c r="B7" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135558533</v>
       </c>
       <c r="B9" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135558956</v>
       </c>
       <c r="B10" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135558472</v>
       </c>
       <c r="B11" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135558865</v>
       </c>
       <c r="B12" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 14786-2026 artfynd.xlsx
+++ b/artfynd/A 14786-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135558676</v>
       </c>
       <c r="B2" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135558885</v>
       </c>
       <c r="B3" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135559348</v>
       </c>
       <c r="B4" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135559561</v>
       </c>
       <c r="B5" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135559640</v>
       </c>
       <c r="B6" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135559895</v>
       </c>
       <c r="B7" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135558813</v>
       </c>
       <c r="B8" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135558533</v>
       </c>
       <c r="B9" t="n">
-        <v>98297</v>
+        <v>98314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135558956</v>
       </c>
       <c r="B10" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135558472</v>
       </c>
       <c r="B11" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135558865</v>
       </c>
       <c r="B12" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 14786-2026 artfynd.xlsx
+++ b/artfynd/A 14786-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135558676</v>
       </c>
       <c r="B2" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135558885</v>
       </c>
       <c r="B3" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135559348</v>
       </c>
       <c r="B4" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135559561</v>
       </c>
       <c r="B5" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135559640</v>
       </c>
       <c r="B6" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135559895</v>
       </c>
       <c r="B7" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135558813</v>
       </c>
       <c r="B8" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135558533</v>
       </c>
       <c r="B9" t="n">
-        <v>98314</v>
+        <v>98315</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135558956</v>
       </c>
       <c r="B10" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135558472</v>
       </c>
       <c r="B11" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135558865</v>
       </c>
       <c r="B12" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 14786-2026 artfynd.xlsx
+++ b/artfynd/A 14786-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135558676</v>
       </c>
       <c r="B2" t="n">
-        <v>97404</v>
+        <v>97405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135558885</v>
       </c>
       <c r="B3" t="n">
-        <v>97404</v>
+        <v>97405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135559348</v>
       </c>
       <c r="B4" t="n">
-        <v>97404</v>
+        <v>97405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135559561</v>
       </c>
       <c r="B5" t="n">
-        <v>97404</v>
+        <v>97405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135559640</v>
       </c>
       <c r="B6" t="n">
-        <v>97404</v>
+        <v>97405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135559895</v>
       </c>
       <c r="B7" t="n">
-        <v>97404</v>
+        <v>97405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135558533</v>
       </c>
       <c r="B9" t="n">
-        <v>98315</v>
+        <v>98316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135558956</v>
       </c>
       <c r="B10" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135558472</v>
       </c>
       <c r="B11" t="n">
-        <v>111269</v>
+        <v>111270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135558865</v>
       </c>
       <c r="B12" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
